--- a/passage_clusters/VIIRS/CLUSTER_1/VCI3M_Forecast_Overview_CLUSTER_1.xlsx
+++ b/passage_clusters/VIIRS/CLUSTER_1/VCI3M_Forecast_Overview_CLUSTER_1.xlsx
@@ -442,37 +442,37 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="B1" s="1">
-        <v>46064</v>
+        <v>45727</v>
       </c>
       <c r="C1" s="1">
-        <v>46071</v>
+        <v>45734</v>
       </c>
       <c r="D1" s="1">
-        <v>46078</v>
+        <v>45741</v>
       </c>
       <c r="E1" s="1">
-        <v>46085</v>
+        <v>45748</v>
       </c>
       <c r="F1" s="1">
-        <v>46092</v>
+        <v>45755</v>
       </c>
       <c r="G1" s="1">
-        <v>46099</v>
+        <v>45762</v>
       </c>
       <c r="H1" s="1">
-        <v>46106</v>
+        <v>45769</v>
       </c>
       <c r="I1" s="1">
-        <v>46113</v>
+        <v>45776</v>
       </c>
       <c r="J1" s="1">
-        <v>46120</v>
+        <v>45783</v>
       </c>
       <c r="K1" s="1">
-        <v>46127</v>
+        <v>45790</v>
       </c>
       <c r="L1" s="1">
-        <v>46134</v>
+        <v>45797</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -480,37 +480,37 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>48.6</v>
+        <v>48.3</v>
       </c>
       <c r="C2">
-        <v>47.7</v>
+        <v>45.1</v>
       </c>
       <c r="D2">
-        <v>46.8</v>
+        <v>42.1</v>
       </c>
       <c r="E2">
-        <v>46</v>
+        <v>39.4</v>
       </c>
       <c r="F2">
-        <v>45.1</v>
+        <v>37.2</v>
       </c>
       <c r="G2">
-        <v>44</v>
+        <v>35.6</v>
       </c>
       <c r="H2">
-        <v>42.9</v>
+        <v>34.4</v>
       </c>
       <c r="I2">
-        <v>41.7</v>
+        <v>33.8</v>
       </c>
       <c r="J2">
-        <v>40.5</v>
+        <v>33.6</v>
       </c>
       <c r="K2">
-        <v>39.2</v>
+        <v>33.9</v>
       </c>
       <c r="L2">
-        <v>38</v>
+        <v>34.6</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -518,37 +518,37 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>61.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="C3">
-        <v>63.9</v>
+        <v>63</v>
       </c>
       <c r="D3">
-        <v>66.3</v>
+        <v>59.6</v>
       </c>
       <c r="E3">
-        <v>68.8</v>
+        <v>55.6</v>
       </c>
       <c r="F3">
-        <v>71.2</v>
+        <v>51</v>
       </c>
       <c r="G3">
-        <v>73.40000000000001</v>
+        <v>46.3</v>
       </c>
       <c r="H3">
-        <v>75.3</v>
+        <v>41.6</v>
       </c>
       <c r="I3">
-        <v>76.7</v>
+        <v>37.2</v>
       </c>
       <c r="J3">
-        <v>77.59999999999999</v>
+        <v>33.3</v>
       </c>
       <c r="K3">
-        <v>77.90000000000001</v>
+        <v>30.1</v>
       </c>
       <c r="L3">
-        <v>77.59999999999999</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -556,37 +556,37 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>35.7</v>
+        <v>30.2</v>
       </c>
       <c r="C4">
-        <v>32.6</v>
+        <v>26.3</v>
       </c>
       <c r="D4">
-        <v>29.6</v>
+        <v>22.6</v>
       </c>
       <c r="E4">
-        <v>26.9</v>
+        <v>19.3</v>
       </c>
       <c r="F4">
-        <v>24.6</v>
+        <v>16.7</v>
       </c>
       <c r="G4">
-        <v>22.5</v>
+        <v>14.7</v>
       </c>
       <c r="H4">
-        <v>20.9</v>
+        <v>13.3</v>
       </c>
       <c r="I4">
-        <v>19.6</v>
+        <v>12.5</v>
       </c>
       <c r="J4">
-        <v>18.7</v>
+        <v>12.3</v>
       </c>
       <c r="K4">
-        <v>18.2</v>
+        <v>12.8</v>
       </c>
       <c r="L4">
-        <v>18.1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -594,37 +594,37 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>57</v>
+        <v>47.7</v>
       </c>
       <c r="C5">
-        <v>56.5</v>
+        <v>44.2</v>
       </c>
       <c r="D5">
-        <v>56.2</v>
+        <v>41</v>
       </c>
       <c r="E5">
-        <v>56</v>
+        <v>38.2</v>
       </c>
       <c r="F5">
-        <v>55.7</v>
+        <v>36</v>
       </c>
       <c r="G5">
-        <v>55.4</v>
+        <v>34.2</v>
       </c>
       <c r="H5">
-        <v>54.8</v>
+        <v>32.9</v>
       </c>
       <c r="I5">
-        <v>54.1</v>
+        <v>32.1</v>
       </c>
       <c r="J5">
-        <v>53.1</v>
+        <v>31.8</v>
       </c>
       <c r="K5">
-        <v>52</v>
+        <v>31.9</v>
       </c>
       <c r="L5">
-        <v>50.7</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -632,37 +632,37 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>46.4</v>
+        <v>66.2</v>
       </c>
       <c r="C6">
-        <v>47</v>
+        <v>64.2</v>
       </c>
       <c r="D6">
-        <v>47.5</v>
+        <v>62.1</v>
       </c>
       <c r="E6">
-        <v>47.6</v>
+        <v>60</v>
       </c>
       <c r="F6">
-        <v>47.1</v>
+        <v>58.2</v>
       </c>
       <c r="G6">
-        <v>45.8</v>
+        <v>56.9</v>
       </c>
       <c r="H6">
-        <v>43.9</v>
+        <v>56</v>
       </c>
       <c r="I6">
-        <v>41.5</v>
+        <v>55.7</v>
       </c>
       <c r="J6">
-        <v>38.5</v>
+        <v>55.7</v>
       </c>
       <c r="K6">
-        <v>35.4</v>
+        <v>56.1</v>
       </c>
       <c r="L6">
-        <v>32.5</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -670,37 +670,37 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>36.4</v>
+        <v>42.2</v>
       </c>
       <c r="C7">
-        <v>36.6</v>
+        <v>39.9</v>
       </c>
       <c r="D7">
-        <v>36.4</v>
+        <v>38.3</v>
       </c>
       <c r="E7">
-        <v>35.6</v>
+        <v>37.4</v>
       </c>
       <c r="F7">
-        <v>34</v>
+        <v>37.5</v>
       </c>
       <c r="G7">
-        <v>31.5</v>
+        <v>38.2</v>
       </c>
       <c r="H7">
-        <v>28.3</v>
+        <v>39.6</v>
       </c>
       <c r="I7">
-        <v>24.5</v>
+        <v>41.5</v>
       </c>
       <c r="J7">
-        <v>20.5</v>
+        <v>43.7</v>
       </c>
       <c r="K7">
-        <v>16.5</v>
+        <v>46.1</v>
       </c>
       <c r="L7">
-        <v>13.1</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -708,37 +708,37 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>60.3</v>
+        <v>52.2</v>
       </c>
       <c r="C8">
-        <v>59.2</v>
+        <v>48.7</v>
       </c>
       <c r="D8">
-        <v>58.1</v>
+        <v>45.5</v>
       </c>
       <c r="E8">
-        <v>57</v>
+        <v>42.7</v>
       </c>
       <c r="F8">
-        <v>55.8</v>
+        <v>40.6</v>
       </c>
       <c r="G8">
-        <v>54.6</v>
+        <v>39.1</v>
       </c>
       <c r="H8">
-        <v>53.3</v>
+        <v>38.1</v>
       </c>
       <c r="I8">
-        <v>51.9</v>
+        <v>37.7</v>
       </c>
       <c r="J8">
-        <v>50.5</v>
+        <v>37.7</v>
       </c>
       <c r="K8">
-        <v>49</v>
+        <v>38.2</v>
       </c>
       <c r="L8">
-        <v>47.6</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -746,37 +746,37 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>46.2</v>
+        <v>39</v>
       </c>
       <c r="C9">
-        <v>45.1</v>
+        <v>36</v>
       </c>
       <c r="D9">
-        <v>44</v>
+        <v>33.7</v>
       </c>
       <c r="E9">
-        <v>42.8</v>
+        <v>32.1</v>
       </c>
       <c r="F9">
-        <v>41.4</v>
+        <v>31.2</v>
       </c>
       <c r="G9">
-        <v>39.8</v>
+        <v>31</v>
       </c>
       <c r="H9">
-        <v>37.8</v>
+        <v>31.4</v>
       </c>
       <c r="I9">
+        <v>32.3</v>
+      </c>
+      <c r="J9">
+        <v>33.7</v>
+      </c>
+      <c r="K9">
         <v>35.5</v>
       </c>
-      <c r="J9">
-        <v>33</v>
-      </c>
-      <c r="K9">
-        <v>30.4</v>
-      </c>
       <c r="L9">
-        <v>28</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -784,37 +784,37 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>51.6</v>
+        <v>36.9</v>
       </c>
       <c r="C10">
-        <v>49</v>
+        <v>34.4</v>
       </c>
       <c r="D10">
-        <v>46.7</v>
+        <v>32.7</v>
       </c>
       <c r="E10">
-        <v>44.9</v>
+        <v>31.9</v>
       </c>
       <c r="F10">
-        <v>43.7</v>
+        <v>32</v>
       </c>
       <c r="G10">
-        <v>43</v>
+        <v>32.7</v>
       </c>
       <c r="H10">
-        <v>42.8</v>
+        <v>34.1</v>
       </c>
       <c r="I10">
+        <v>36</v>
+      </c>
+      <c r="J10">
+        <v>38.2</v>
+      </c>
+      <c r="K10">
+        <v>40.6</v>
+      </c>
+      <c r="L10">
         <v>43.1</v>
-      </c>
-      <c r="J10">
-        <v>43.7</v>
-      </c>
-      <c r="K10">
-        <v>44.5</v>
-      </c>
-      <c r="L10">
-        <v>45.5</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -822,37 +822,37 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>61.2</v>
+        <v>52.3</v>
       </c>
       <c r="C11">
-        <v>60.6</v>
+        <v>48.7</v>
       </c>
       <c r="D11">
-        <v>60.1</v>
+        <v>45.5</v>
       </c>
       <c r="E11">
-        <v>59.6</v>
+        <v>42.9</v>
       </c>
       <c r="F11">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="G11">
-        <v>58.3</v>
+        <v>39.7</v>
       </c>
       <c r="H11">
-        <v>57.4</v>
+        <v>38.8</v>
       </c>
       <c r="I11">
-        <v>56.2</v>
+        <v>38.6</v>
       </c>
       <c r="J11">
-        <v>54.8</v>
+        <v>38.8</v>
       </c>
       <c r="K11">
-        <v>53.2</v>
+        <v>39.4</v>
       </c>
       <c r="L11">
-        <v>51.5</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -860,37 +860,37 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>61.3</v>
+        <v>56.6</v>
       </c>
       <c r="C12">
-        <v>61.5</v>
+        <v>53</v>
       </c>
       <c r="D12">
-        <v>62</v>
+        <v>49.5</v>
       </c>
       <c r="E12">
-        <v>62.6</v>
+        <v>46.3</v>
       </c>
       <c r="F12">
-        <v>63.5</v>
+        <v>43.5</v>
       </c>
       <c r="G12">
-        <v>64.40000000000001</v>
+        <v>41.2</v>
       </c>
       <c r="H12">
-        <v>65.3</v>
+        <v>39.2</v>
       </c>
       <c r="I12">
-        <v>66.2</v>
+        <v>37.8</v>
       </c>
       <c r="J12">
-        <v>66.90000000000001</v>
+        <v>36.7</v>
       </c>
       <c r="K12">
-        <v>67.3</v>
+        <v>36.1</v>
       </c>
       <c r="L12">
-        <v>67.40000000000001</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -898,37 +898,37 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>61.2</v>
+        <v>59.1</v>
       </c>
       <c r="C13">
-        <v>61.6</v>
+        <v>56.4</v>
       </c>
       <c r="D13">
-        <v>62.3</v>
+        <v>53.7</v>
       </c>
       <c r="E13">
-        <v>63.2</v>
+        <v>50.9</v>
       </c>
       <c r="F13">
-        <v>64.3</v>
+        <v>48.3</v>
       </c>
       <c r="G13">
-        <v>65.59999999999999</v>
+        <v>46</v>
       </c>
       <c r="H13">
-        <v>66.8</v>
+        <v>43.8</v>
       </c>
       <c r="I13">
-        <v>67.8</v>
+        <v>42</v>
       </c>
       <c r="J13">
-        <v>68.5</v>
+        <v>40.6</v>
       </c>
       <c r="K13">
-        <v>69</v>
+        <v>39.6</v>
       </c>
       <c r="L13">
-        <v>69</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -936,37 +936,37 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>31.6</v>
+        <v>43.7</v>
       </c>
       <c r="C14">
-        <v>30.2</v>
+        <v>41</v>
       </c>
       <c r="D14">
-        <v>28.9</v>
+        <v>38.4</v>
       </c>
       <c r="E14">
-        <v>27.8</v>
+        <v>36.2</v>
       </c>
       <c r="F14">
-        <v>26.8</v>
+        <v>34.4</v>
       </c>
       <c r="G14">
-        <v>25.9</v>
+        <v>33.1</v>
       </c>
       <c r="H14">
-        <v>25.2</v>
+        <v>32.3</v>
       </c>
       <c r="I14">
-        <v>24.7</v>
+        <v>32</v>
       </c>
       <c r="J14">
-        <v>24.4</v>
+        <v>32.1</v>
       </c>
       <c r="K14">
-        <v>24.4</v>
+        <v>32.6</v>
       </c>
       <c r="L14">
-        <v>24.6</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -974,37 +974,37 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>33</v>
+        <v>37.9</v>
       </c>
       <c r="C15">
-        <v>30.3</v>
+        <v>34</v>
       </c>
       <c r="D15">
-        <v>28</v>
+        <v>30.6</v>
       </c>
       <c r="E15">
-        <v>26.1</v>
+        <v>27.8</v>
       </c>
       <c r="F15">
-        <v>24.7</v>
+        <v>25.6</v>
       </c>
       <c r="G15">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="H15">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="I15">
-        <v>22.8</v>
+        <v>21.8</v>
       </c>
       <c r="J15">
-        <v>22.8</v>
+        <v>21.2</v>
       </c>
       <c r="K15">
-        <v>23.1</v>
+        <v>21</v>
       </c>
       <c r="L15">
-        <v>23.6</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1012,37 +1012,37 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>49.4</v>
+        <v>48.6</v>
       </c>
       <c r="C16">
-        <v>48.2</v>
+        <v>44.8</v>
       </c>
       <c r="D16">
-        <v>46.9</v>
+        <v>40.8</v>
       </c>
       <c r="E16">
-        <v>45.5</v>
+        <v>37</v>
       </c>
       <c r="F16">
-        <v>43.9</v>
+        <v>33.4</v>
       </c>
       <c r="G16">
-        <v>42.2</v>
+        <v>30.1</v>
       </c>
       <c r="H16">
-        <v>40.4</v>
+        <v>27.2</v>
       </c>
       <c r="I16">
-        <v>38.5</v>
+        <v>24.8</v>
       </c>
       <c r="J16">
-        <v>36.6</v>
+        <v>23</v>
       </c>
       <c r="K16">
-        <v>34.7</v>
+        <v>21.9</v>
       </c>
       <c r="L16">
-        <v>33.1</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1050,37 +1050,37 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>52.9</v>
+        <v>55</v>
       </c>
       <c r="C17">
-        <v>52.3</v>
+        <v>50.9</v>
       </c>
       <c r="D17">
-        <v>51.5</v>
+        <v>46.7</v>
       </c>
       <c r="E17">
-        <v>50.7</v>
+        <v>42.6</v>
       </c>
       <c r="F17">
-        <v>49.7</v>
+        <v>38.7</v>
       </c>
       <c r="G17">
-        <v>48.5</v>
+        <v>35.3</v>
       </c>
       <c r="H17">
-        <v>47.2</v>
+        <v>32.3</v>
       </c>
       <c r="I17">
-        <v>45.8</v>
+        <v>29.9</v>
       </c>
       <c r="J17">
-        <v>44.3</v>
+        <v>28.1</v>
       </c>
       <c r="K17">
-        <v>42.8</v>
+        <v>27</v>
       </c>
       <c r="L17">
-        <v>41.3</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1088,37 +1088,37 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>53.2</v>
+        <v>42.3</v>
       </c>
       <c r="C18">
-        <v>51.8</v>
+        <v>38.6</v>
       </c>
       <c r="D18">
-        <v>50.2</v>
+        <v>35.3</v>
       </c>
       <c r="E18">
-        <v>48.3</v>
+        <v>32.4</v>
       </c>
       <c r="F18">
-        <v>46</v>
+        <v>30.1</v>
       </c>
       <c r="G18">
-        <v>43.4</v>
+        <v>28.3</v>
       </c>
       <c r="H18">
-        <v>40.6</v>
+        <v>27.1</v>
       </c>
       <c r="I18">
-        <v>37.7</v>
+        <v>26.4</v>
       </c>
       <c r="J18">
-        <v>34.7</v>
+        <v>26.3</v>
       </c>
       <c r="K18">
-        <v>32</v>
+        <v>26.7</v>
       </c>
       <c r="L18">
-        <v>29.6</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1126,37 +1126,37 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>40.3</v>
+        <v>53.9</v>
       </c>
       <c r="C19">
-        <v>39.8</v>
+        <v>51.3</v>
       </c>
       <c r="D19">
-        <v>39.3</v>
+        <v>48.7</v>
       </c>
       <c r="E19">
-        <v>38.5</v>
+        <v>46.4</v>
       </c>
       <c r="F19">
-        <v>37.3</v>
+        <v>44.5</v>
       </c>
       <c r="G19">
-        <v>35.7</v>
+        <v>43.2</v>
       </c>
       <c r="H19">
-        <v>33.9</v>
+        <v>42.6</v>
       </c>
       <c r="I19">
-        <v>31.8</v>
+        <v>42.7</v>
       </c>
       <c r="J19">
-        <v>29.7</v>
+        <v>43.2</v>
       </c>
       <c r="K19">
-        <v>27.7</v>
+        <v>44.2</v>
       </c>
       <c r="L19">
-        <v>26</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1164,37 +1164,37 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>42.2</v>
+        <v>46.8</v>
       </c>
       <c r="C20">
+        <v>43.3</v>
+      </c>
+      <c r="D20">
+        <v>40.2</v>
+      </c>
+      <c r="E20">
+        <v>37.7</v>
+      </c>
+      <c r="F20">
+        <v>36</v>
+      </c>
+      <c r="G20">
+        <v>35.1</v>
+      </c>
+      <c r="H20">
+        <v>35.1</v>
+      </c>
+      <c r="I20">
+        <v>35.8</v>
+      </c>
+      <c r="J20">
+        <v>37.2</v>
+      </c>
+      <c r="K20">
+        <v>39</v>
+      </c>
+      <c r="L20">
         <v>41.2</v>
-      </c>
-      <c r="D20">
-        <v>40</v>
-      </c>
-      <c r="E20">
-        <v>38.6</v>
-      </c>
-      <c r="F20">
-        <v>36.8</v>
-      </c>
-      <c r="G20">
-        <v>34.7</v>
-      </c>
-      <c r="H20">
-        <v>32.4</v>
-      </c>
-      <c r="I20">
-        <v>29.8</v>
-      </c>
-      <c r="J20">
-        <v>27.1</v>
-      </c>
-      <c r="K20">
-        <v>24.4</v>
-      </c>
-      <c r="L20">
-        <v>22.1</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1202,37 +1202,37 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>41.2</v>
+        <v>42</v>
       </c>
       <c r="C21">
-        <v>38.5</v>
+        <v>38.3</v>
       </c>
       <c r="D21">
-        <v>35.9</v>
+        <v>34.7</v>
       </c>
       <c r="E21">
-        <v>33.2</v>
+        <v>31.5</v>
       </c>
       <c r="F21">
-        <v>30.7</v>
+        <v>29</v>
       </c>
       <c r="G21">
-        <v>28.4</v>
+        <v>27</v>
       </c>
       <c r="H21">
-        <v>26.4</v>
+        <v>25.7</v>
       </c>
       <c r="I21">
-        <v>24.6</v>
+        <v>25.1</v>
       </c>
       <c r="J21">
-        <v>23.2</v>
+        <v>25</v>
       </c>
       <c r="K21">
-        <v>22.1</v>
+        <v>25.6</v>
       </c>
       <c r="L21">
-        <v>21.5</v>
+        <v>26.6</v>
       </c>
     </row>
   </sheetData>

--- a/passage_clusters/VIIRS/CLUSTER_1/VCI3M_Forecast_Overview_CLUSTER_1.xlsx
+++ b/passage_clusters/VIIRS/CLUSTER_1/VCI3M_Forecast_Overview_CLUSTER_1.xlsx
@@ -442,37 +442,37 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="B1" s="1">
-        <v>45727</v>
+        <v>46078</v>
       </c>
       <c r="C1" s="1">
-        <v>45734</v>
+        <v>46085</v>
       </c>
       <c r="D1" s="1">
-        <v>45741</v>
+        <v>46092</v>
       </c>
       <c r="E1" s="1">
-        <v>45748</v>
+        <v>46099</v>
       </c>
       <c r="F1" s="1">
-        <v>45755</v>
+        <v>46106</v>
       </c>
       <c r="G1" s="1">
-        <v>45762</v>
+        <v>46113</v>
       </c>
       <c r="H1" s="1">
-        <v>45769</v>
+        <v>46120</v>
       </c>
       <c r="I1" s="1">
-        <v>45776</v>
+        <v>46127</v>
       </c>
       <c r="J1" s="1">
-        <v>45783</v>
+        <v>46134</v>
       </c>
       <c r="K1" s="1">
-        <v>45790</v>
+        <v>46141</v>
       </c>
       <c r="L1" s="1">
-        <v>45797</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -480,37 +480,37 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>48.3</v>
+        <v>47.7</v>
       </c>
       <c r="C2">
-        <v>45.1</v>
+        <v>47.6</v>
       </c>
       <c r="D2">
-        <v>42.1</v>
+        <v>47.8</v>
       </c>
       <c r="E2">
-        <v>39.4</v>
+        <v>48.2</v>
       </c>
       <c r="F2">
-        <v>37.2</v>
+        <v>48.8</v>
       </c>
       <c r="G2">
-        <v>35.6</v>
+        <v>49.5</v>
       </c>
       <c r="H2">
-        <v>34.4</v>
+        <v>50.2</v>
       </c>
       <c r="I2">
-        <v>33.8</v>
+        <v>51</v>
       </c>
       <c r="J2">
-        <v>33.6</v>
+        <v>51.8</v>
       </c>
       <c r="K2">
-        <v>33.9</v>
+        <v>52.7</v>
       </c>
       <c r="L2">
-        <v>34.6</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -518,37 +518,37 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>65.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="C3">
-        <v>63</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="D3">
-        <v>59.6</v>
+        <v>75.8</v>
       </c>
       <c r="E3">
-        <v>55.6</v>
+        <v>80.2</v>
       </c>
       <c r="F3">
-        <v>51</v>
+        <v>84.8</v>
       </c>
       <c r="G3">
-        <v>46.3</v>
+        <v>89.2</v>
       </c>
       <c r="H3">
-        <v>41.6</v>
+        <v>93.2</v>
       </c>
       <c r="I3">
-        <v>37.2</v>
+        <v>96.7</v>
       </c>
       <c r="J3">
-        <v>33.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="K3">
-        <v>30.1</v>
+        <v>101.3</v>
       </c>
       <c r="L3">
-        <v>27.8</v>
+        <v>102.2</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -556,37 +556,37 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>30.2</v>
+        <v>30.7</v>
       </c>
       <c r="C4">
-        <v>26.3</v>
+        <v>29.1</v>
       </c>
       <c r="D4">
-        <v>22.6</v>
+        <v>28.2</v>
       </c>
       <c r="E4">
-        <v>19.3</v>
+        <v>28.2</v>
       </c>
       <c r="F4">
-        <v>16.7</v>
+        <v>28.9</v>
       </c>
       <c r="G4">
-        <v>14.7</v>
+        <v>30.3</v>
       </c>
       <c r="H4">
-        <v>13.3</v>
+        <v>32.3</v>
       </c>
       <c r="I4">
-        <v>12.5</v>
+        <v>34.8</v>
       </c>
       <c r="J4">
-        <v>12.3</v>
+        <v>37.6</v>
       </c>
       <c r="K4">
-        <v>12.8</v>
+        <v>40.6</v>
       </c>
       <c r="L4">
-        <v>14</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -594,37 +594,37 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>47.7</v>
+        <v>56.4</v>
       </c>
       <c r="C5">
-        <v>44.2</v>
+        <v>56.4</v>
       </c>
       <c r="D5">
-        <v>41</v>
+        <v>56.3</v>
       </c>
       <c r="E5">
-        <v>38.2</v>
+        <v>56.3</v>
       </c>
       <c r="F5">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="G5">
-        <v>34.2</v>
+        <v>55.7</v>
       </c>
       <c r="H5">
-        <v>32.9</v>
+        <v>55</v>
       </c>
       <c r="I5">
-        <v>32.1</v>
+        <v>54.2</v>
       </c>
       <c r="J5">
-        <v>31.8</v>
+        <v>53.3</v>
       </c>
       <c r="K5">
-        <v>31.9</v>
+        <v>52.2</v>
       </c>
       <c r="L5">
-        <v>32.4</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -632,37 +632,37 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>66.2</v>
+        <v>48.1</v>
       </c>
       <c r="C6">
-        <v>64.2</v>
+        <v>48.7</v>
       </c>
       <c r="D6">
-        <v>62.1</v>
+        <v>49</v>
       </c>
       <c r="E6">
-        <v>60</v>
+        <v>48.8</v>
       </c>
       <c r="F6">
-        <v>58.2</v>
+        <v>48.2</v>
       </c>
       <c r="G6">
-        <v>56.9</v>
+        <v>47.1</v>
       </c>
       <c r="H6">
-        <v>56</v>
+        <v>45.7</v>
       </c>
       <c r="I6">
-        <v>55.7</v>
+        <v>44.2</v>
       </c>
       <c r="J6">
-        <v>55.7</v>
+        <v>42.7</v>
       </c>
       <c r="K6">
-        <v>56.1</v>
+        <v>41.4</v>
       </c>
       <c r="L6">
-        <v>56.6</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -670,37 +670,37 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>42.2</v>
+        <v>38.2</v>
       </c>
       <c r="C7">
-        <v>39.9</v>
+        <v>39.1</v>
       </c>
       <c r="D7">
-        <v>38.3</v>
+        <v>39.8</v>
       </c>
       <c r="E7">
-        <v>37.4</v>
+        <v>40.3</v>
       </c>
       <c r="F7">
-        <v>37.5</v>
+        <v>40.7</v>
       </c>
       <c r="G7">
-        <v>38.2</v>
+        <v>41</v>
       </c>
       <c r="H7">
-        <v>39.6</v>
+        <v>41.3</v>
       </c>
       <c r="I7">
-        <v>41.5</v>
+        <v>41.9</v>
       </c>
       <c r="J7">
-        <v>43.7</v>
+        <v>42.9</v>
       </c>
       <c r="K7">
+        <v>44.3</v>
+      </c>
+      <c r="L7">
         <v>46.1</v>
-      </c>
-      <c r="L7">
-        <v>48.4</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -708,37 +708,37 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>52.2</v>
+        <v>58.9</v>
       </c>
       <c r="C8">
-        <v>48.7</v>
+        <v>58.5</v>
       </c>
       <c r="D8">
-        <v>45.5</v>
+        <v>58.2</v>
       </c>
       <c r="E8">
-        <v>42.7</v>
+        <v>58.2</v>
       </c>
       <c r="F8">
-        <v>40.6</v>
+        <v>58.2</v>
       </c>
       <c r="G8">
-        <v>39.1</v>
+        <v>58.3</v>
       </c>
       <c r="H8">
-        <v>38.1</v>
+        <v>58.4</v>
       </c>
       <c r="I8">
-        <v>37.7</v>
+        <v>58.5</v>
       </c>
       <c r="J8">
-        <v>37.7</v>
+        <v>58.6</v>
       </c>
       <c r="K8">
-        <v>38.2</v>
+        <v>58.7</v>
       </c>
       <c r="L8">
-        <v>39</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -746,37 +746,37 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>39</v>
+        <v>44.6</v>
       </c>
       <c r="C9">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D9">
-        <v>33.7</v>
+        <v>43.4</v>
       </c>
       <c r="E9">
-        <v>32.1</v>
+        <v>42.8</v>
       </c>
       <c r="F9">
-        <v>31.2</v>
+        <v>41.9</v>
       </c>
       <c r="G9">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H9">
-        <v>31.4</v>
+        <v>39.8</v>
       </c>
       <c r="I9">
-        <v>32.3</v>
+        <v>38.7</v>
       </c>
       <c r="J9">
-        <v>33.7</v>
+        <v>37.6</v>
       </c>
       <c r="K9">
-        <v>35.5</v>
+        <v>36.8</v>
       </c>
       <c r="L9">
-        <v>37.5</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -784,37 +784,37 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>36.9</v>
+        <v>46.8</v>
       </c>
       <c r="C10">
-        <v>34.4</v>
+        <v>45</v>
       </c>
       <c r="D10">
-        <v>32.7</v>
+        <v>43.8</v>
       </c>
       <c r="E10">
-        <v>31.9</v>
+        <v>43.1</v>
       </c>
       <c r="F10">
-        <v>32</v>
+        <v>42.8</v>
       </c>
       <c r="G10">
-        <v>32.7</v>
+        <v>43</v>
       </c>
       <c r="H10">
-        <v>34.1</v>
+        <v>43.5</v>
       </c>
       <c r="I10">
-        <v>36</v>
+        <v>44.2</v>
       </c>
       <c r="J10">
-        <v>38.2</v>
+        <v>44.9</v>
       </c>
       <c r="K10">
-        <v>40.6</v>
+        <v>45.6</v>
       </c>
       <c r="L10">
-        <v>43.1</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -822,37 +822,37 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>52.3</v>
+        <v>60.4</v>
       </c>
       <c r="C11">
-        <v>48.7</v>
+        <v>60</v>
       </c>
       <c r="D11">
-        <v>45.5</v>
+        <v>59.7</v>
       </c>
       <c r="E11">
-        <v>42.9</v>
+        <v>59.2</v>
       </c>
       <c r="F11">
-        <v>41</v>
+        <v>58.5</v>
       </c>
       <c r="G11">
-        <v>39.7</v>
+        <v>57.5</v>
       </c>
       <c r="H11">
-        <v>38.8</v>
+        <v>56.3</v>
       </c>
       <c r="I11">
-        <v>38.6</v>
+        <v>54.9</v>
       </c>
       <c r="J11">
-        <v>38.8</v>
+        <v>53.4</v>
       </c>
       <c r="K11">
-        <v>39.4</v>
+        <v>51.8</v>
       </c>
       <c r="L11">
-        <v>40.4</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -860,37 +860,37 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>56.6</v>
+        <v>62.7</v>
       </c>
       <c r="C12">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="D12">
-        <v>49.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E12">
-        <v>46.3</v>
+        <v>67.5</v>
       </c>
       <c r="F12">
-        <v>43.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="G12">
-        <v>41.2</v>
+        <v>71.7</v>
       </c>
       <c r="H12">
-        <v>39.2</v>
+        <v>73.7</v>
       </c>
       <c r="I12">
-        <v>37.8</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="J12">
-        <v>36.7</v>
+        <v>76.8</v>
       </c>
       <c r="K12">
-        <v>36.1</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="L12">
-        <v>36</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -898,37 +898,37 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>59.1</v>
+        <v>63.4</v>
       </c>
       <c r="C13">
-        <v>56.4</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D13">
-        <v>53.7</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="E13">
-        <v>50.9</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F13">
-        <v>48.3</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="G13">
-        <v>46</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="H13">
-        <v>43.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I13">
-        <v>42</v>
+        <v>83.5</v>
       </c>
       <c r="J13">
-        <v>40.6</v>
+        <v>85.8</v>
       </c>
       <c r="K13">
-        <v>39.6</v>
+        <v>87.5</v>
       </c>
       <c r="L13">
-        <v>39.1</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -936,37 +936,37 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>43.7</v>
+        <v>29.6</v>
       </c>
       <c r="C14">
-        <v>41</v>
+        <v>29.1</v>
       </c>
       <c r="D14">
-        <v>38.4</v>
+        <v>28.9</v>
       </c>
       <c r="E14">
-        <v>36.2</v>
+        <v>29.2</v>
       </c>
       <c r="F14">
-        <v>34.4</v>
+        <v>29.8</v>
       </c>
       <c r="G14">
-        <v>33.1</v>
+        <v>30.8</v>
       </c>
       <c r="H14">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="I14">
-        <v>32</v>
+        <v>33.9</v>
       </c>
       <c r="J14">
-        <v>32.1</v>
+        <v>35.8</v>
       </c>
       <c r="K14">
-        <v>32.6</v>
+        <v>37.8</v>
       </c>
       <c r="L14">
-        <v>33.4</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -974,37 +974,37 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>37.9</v>
+        <v>28.8</v>
       </c>
       <c r="C15">
-        <v>34</v>
+        <v>27.6</v>
       </c>
       <c r="D15">
-        <v>30.6</v>
+        <v>27.2</v>
       </c>
       <c r="E15">
-        <v>27.8</v>
+        <v>27.6</v>
       </c>
       <c r="F15">
-        <v>25.6</v>
+        <v>28.5</v>
       </c>
       <c r="G15">
-        <v>23.9</v>
+        <v>30</v>
       </c>
       <c r="H15">
-        <v>22.7</v>
+        <v>31.9</v>
       </c>
       <c r="I15">
-        <v>21.8</v>
+        <v>34.1</v>
       </c>
       <c r="J15">
-        <v>21.2</v>
+        <v>36.5</v>
       </c>
       <c r="K15">
-        <v>21</v>
+        <v>38.9</v>
       </c>
       <c r="L15">
-        <v>21.2</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1012,37 +1012,37 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="C16">
-        <v>44.8</v>
+        <v>49.1</v>
       </c>
       <c r="D16">
-        <v>40.8</v>
+        <v>50</v>
       </c>
       <c r="E16">
-        <v>37</v>
+        <v>51.5</v>
       </c>
       <c r="F16">
-        <v>33.4</v>
+        <v>53.5</v>
       </c>
       <c r="G16">
-        <v>30.1</v>
+        <v>55.9</v>
       </c>
       <c r="H16">
-        <v>27.2</v>
+        <v>58.6</v>
       </c>
       <c r="I16">
-        <v>24.8</v>
+        <v>61.6</v>
       </c>
       <c r="J16">
-        <v>23</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="K16">
-        <v>21.9</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="L16">
-        <v>21.4</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1050,37 +1050,37 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>55</v>
+        <v>52.8</v>
       </c>
       <c r="C17">
-        <v>50.9</v>
+        <v>53.1</v>
       </c>
       <c r="D17">
-        <v>46.7</v>
+        <v>53.9</v>
       </c>
       <c r="E17">
-        <v>42.6</v>
+        <v>54.9</v>
       </c>
       <c r="F17">
-        <v>38.7</v>
+        <v>56.3</v>
       </c>
       <c r="G17">
-        <v>35.3</v>
+        <v>57.9</v>
       </c>
       <c r="H17">
-        <v>32.3</v>
+        <v>59.7</v>
       </c>
       <c r="I17">
-        <v>29.9</v>
+        <v>61.6</v>
       </c>
       <c r="J17">
-        <v>28.1</v>
+        <v>63.4</v>
       </c>
       <c r="K17">
-        <v>27</v>
+        <v>65.2</v>
       </c>
       <c r="L17">
-        <v>26.7</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1088,37 +1088,37 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>42.3</v>
+        <v>50.6</v>
       </c>
       <c r="C18">
-        <v>38.6</v>
+        <v>48.9</v>
       </c>
       <c r="D18">
-        <v>35.3</v>
+        <v>47</v>
       </c>
       <c r="E18">
-        <v>32.4</v>
+        <v>44.9</v>
       </c>
       <c r="F18">
-        <v>30.1</v>
+        <v>42.6</v>
       </c>
       <c r="G18">
-        <v>28.3</v>
+        <v>40.3</v>
       </c>
       <c r="H18">
-        <v>27.1</v>
+        <v>37.9</v>
       </c>
       <c r="I18">
-        <v>26.4</v>
+        <v>35.7</v>
       </c>
       <c r="J18">
-        <v>26.3</v>
+        <v>33.9</v>
       </c>
       <c r="K18">
-        <v>26.7</v>
+        <v>32.5</v>
       </c>
       <c r="L18">
-        <v>27.5</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1126,37 +1126,37 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>53.9</v>
+        <v>40.3</v>
       </c>
       <c r="C19">
-        <v>51.3</v>
+        <v>40.4</v>
       </c>
       <c r="D19">
-        <v>48.7</v>
+        <v>40.6</v>
       </c>
       <c r="E19">
-        <v>46.4</v>
+        <v>40.8</v>
       </c>
       <c r="F19">
-        <v>44.5</v>
+        <v>41</v>
       </c>
       <c r="G19">
-        <v>43.2</v>
+        <v>41.3</v>
       </c>
       <c r="H19">
-        <v>42.6</v>
+        <v>41.7</v>
       </c>
       <c r="I19">
-        <v>42.7</v>
+        <v>42.4</v>
       </c>
       <c r="J19">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="K19">
-        <v>44.2</v>
+        <v>44.3</v>
       </c>
       <c r="L19">
-        <v>45.4</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1164,37 +1164,37 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>46.8</v>
+        <v>40.7</v>
       </c>
       <c r="C20">
-        <v>43.3</v>
+        <v>40</v>
       </c>
       <c r="D20">
-        <v>40.2</v>
+        <v>39.3</v>
       </c>
       <c r="E20">
-        <v>37.7</v>
+        <v>38.4</v>
       </c>
       <c r="F20">
-        <v>36</v>
+        <v>37.6</v>
       </c>
       <c r="G20">
+        <v>36.7</v>
+      </c>
+      <c r="H20">
+        <v>35.8</v>
+      </c>
+      <c r="I20">
         <v>35.1</v>
       </c>
-      <c r="H20">
-        <v>35.1</v>
-      </c>
-      <c r="I20">
-        <v>35.8</v>
-      </c>
       <c r="J20">
-        <v>37.2</v>
+        <v>34.5</v>
       </c>
       <c r="K20">
-        <v>39</v>
+        <v>34.3</v>
       </c>
       <c r="L20">
-        <v>41.2</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1202,37 +1202,37 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>42</v>
+        <v>36.8</v>
       </c>
       <c r="C21">
-        <v>38.3</v>
+        <v>35.2</v>
       </c>
       <c r="D21">
-        <v>34.7</v>
+        <v>34.2</v>
       </c>
       <c r="E21">
-        <v>31.5</v>
+        <v>33.7</v>
       </c>
       <c r="F21">
-        <v>29</v>
+        <v>33.9</v>
       </c>
       <c r="G21">
-        <v>27</v>
+        <v>34.6</v>
       </c>
       <c r="H21">
-        <v>25.7</v>
+        <v>36</v>
       </c>
       <c r="I21">
-        <v>25.1</v>
+        <v>37.8</v>
       </c>
       <c r="J21">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="K21">
-        <v>25.6</v>
+        <v>42.4</v>
       </c>
       <c r="L21">
-        <v>26.6</v>
+        <v>44.9</v>
       </c>
     </row>
   </sheetData>
